--- a/data-manipulation-scripts/sheets-cleanup/sheets/CACHIMBO - 01_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/CACHIMBO - 01_02.xlsx
@@ -28,61 +28,61 @@
     <t>7898485613166</t>
   </si>
   <si>
-    <t>CACHIMBO VELAMAGNETRON TITAN CG150/ NXR125-150 90250720</t>
+    <t>CACHIMBO VELA MAGNETRON TITAN CG150/ NXR125-150 90250720</t>
   </si>
   <si>
     <t>7893986203069</t>
   </si>
   <si>
-    <t>CACHIMBO VELAPEÇA+ CBX250</t>
+    <t>CACHIMBO VELA PEÇA+ CBX250</t>
   </si>
   <si>
     <t>7897707500017</t>
   </si>
   <si>
-    <t>CACHIMBO VELANGK SD05FMGC</t>
+    <t>CACHIMBO VELA NGK SD05FMGC</t>
   </si>
   <si>
     <t>7898485613159</t>
   </si>
   <si>
-    <t>CACHIMBO VELAMAGNETRON CBX250 2001 A 2008/ CB300 2013 A 2015/ XR250 90250710</t>
+    <t>CACHIMBO VELA MAGNETRON CBX250 2001 A 2008/ CB300 2013 A 2015/ XR250 90250710</t>
   </si>
   <si>
     <t>7898508619076</t>
   </si>
   <si>
-    <t>CACHIMBO VELAMAGNETRON TITAN CG FAN150 2014 A 2015/ FAN160 START 2016 90250930</t>
+    <t>CACHIMBO VELA MAGNETRON TITAN CG FAN150 2014 A 2015/ FAN160 START 2016 90250930</t>
   </si>
   <si>
     <t>7898485613067</t>
   </si>
   <si>
-    <t>CACHIMBO VELAMAGNETRON BIZ100 2005/ CBX200 STRADA/ CG TITAN 1989 90250440</t>
+    <t>CACHIMBO VELA MAGNETRON BIZ100 2005/ CBX200 STRADA/ CG TITAN 1989 90250440</t>
   </si>
   <si>
     <t>7898485613265</t>
   </si>
   <si>
-    <t>CACHIMBO VELAMAGNETRON FAN 2009 A 2015/ POP110 2016 A 2024 90250830</t>
+    <t>CACHIMBO VELA MAGNETRON FAN 2009 A 2015/ POP110 2016 A 2024 90250830</t>
   </si>
   <si>
     <t>751320979025</t>
   </si>
   <si>
-    <t xml:space="preserve"> CACHIMBO VELAIRON CG TITAN FAN 120478</t>
+    <t xml:space="preserve"> CACHIMBO VELA IRON CG TITAN FAN 120478</t>
   </si>
   <si>
     <t>751320979049</t>
   </si>
   <si>
-    <t>CACHIMBO VELAIRON CBX250/ XR250 176314</t>
+    <t>CACHIMBO VELA IRON CBX250/ XR250 176314</t>
   </si>
   <si>
     <t>602883767102</t>
   </si>
   <si>
-    <t>CACHIMBO VELAIRON FAZER150/ XTZ150 YBR150/ FACTOR150 188236</t>
+    <t>CACHIMBO VELA IRON FAZER150/ XTZ150 YBR150/ FACTOR150 188236</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>

--- a/data-manipulation-scripts/sheets-cleanup/sheets/CACHIMBO - 01_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/CACHIMBO - 01_02.xlsx
@@ -391,7 +391,9 @@
       <c r="C2" s="2">
         <v>2.0</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" s="2">
+        <v>30.0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
@@ -487,7 +489,9 @@
       <c r="C9" s="2">
         <v>1.0</v>
       </c>
-      <c r="D9" s="3"/>
+      <c r="D9" s="2">
+        <v>17.0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
@@ -513,7 +517,9 @@
       <c r="C11" s="2">
         <v>8.0</v>
       </c>
-      <c r="D11" s="3"/>
+      <c r="D11" s="2">
+        <v>20.0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
